--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B163501-4DE6-45DE-B416-17967A7B6446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31989AE-F2D0-403C-BEB6-794538A31969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="1905" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13215" yWindow="2670" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>key</t>
   </si>
@@ -226,15 +226,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Bookshelf</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>It's a brick to throw somewhere.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>어딘가에 던질만한 물건이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drum can</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>드럼통</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>드럼통이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Box</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is a box.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is a drum can.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박스이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -245,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +300,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222225"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -290,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -301,6 +345,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -581,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -800,12 +845,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>10071</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>51</v>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>39</v>
@@ -819,7 +864,7 @@
         <v>10072</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>31</v>
@@ -830,85 +875,135 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>11011</v>
+        <v>10081</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>11012</v>
+        <v>10082</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>11021</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>11011</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>11022</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>11012</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>12011</v>
+        <v>11021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
+        <v>11022</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>12011</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>12012</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31989AE-F2D0-403C-BEB6-794538A31969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0B51CB-67D7-4528-ADE1-883330C4FD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13215" yWindow="2670" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -903,7 +903,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>11011</v>
+        <v>10091</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>58</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>11012</v>
+        <v>10092</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>58</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>11021</v>
+        <v>11011</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>40</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>11022</v>
+        <v>11012</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>40</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>12011</v>
+        <v>11021</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>45</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>12012</v>
+        <v>11022</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>45</v>
@@ -986,6 +986,9 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>12011</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
@@ -997,6 +1000,9 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>12012</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0B51CB-67D7-4528-ADE1-883330C4FD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E569A3-47DD-4940-AB7C-791496739500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>key</t>
   </si>
@@ -272,6 +272,9 @@
   <si>
     <t>박스이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropaneTank</t>
   </si>
 </sst>
 </file>
@@ -281,7 +284,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +316,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF27262E"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -334,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,6 +357,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -626,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -1013,6 +1025,34 @@
         <v>17</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>12021</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>12022</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E569A3-47DD-4940-AB7C-791496739500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF63CA3-83C8-4339-B4B1-16153CBE3C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14760" yWindow="1905" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>key</t>
   </si>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사물함</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>탁자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -60,14 +56,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>This is a cabinet.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>사물함이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>This is a table.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -108,10 +96,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이상한 물건</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>어딘가 이상한 물건이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -120,34 +104,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>도어락</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This is an electronic door lock</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>도어락이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 공간의 지도로 보인다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>It looks like a map of this space.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>책장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>If it falls, it will block the corridor.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -156,10 +112,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cabinet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Table</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -172,18 +124,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Electronic door lock</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bookshelf</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Tablet</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -242,10 +182,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Drum can</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>드럼통</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -254,27 +190,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Box</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This is a box.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This is a drum can.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박스이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PropaneTank</t>
+  </si>
+  <si>
+    <t>DrumBarrel</t>
+  </si>
+  <si>
+    <t>This is a drum barrel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상한 물건 이거부숴지는거..</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>판자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is a Key.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>열쇠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>열쇠이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -638,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -652,13 +603,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -666,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -680,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -694,13 +645,13 @@
         <v>10011</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -708,13 +659,13 @@
         <v>10012</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -722,13 +673,13 @@
         <v>10021</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -736,13 +687,13 @@
         <v>10022</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -750,13 +701,13 @@
         <v>10031</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -764,13 +715,13 @@
         <v>10032</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -778,13 +729,13 @@
         <v>10041</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -792,27 +743,27 @@
         <v>10042</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10051</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -820,237 +771,153 @@
         <v>10052</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>10061</v>
+        <v>11011</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>10062</v>
+        <v>11012</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>11021</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>10071</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>10072</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>11022</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>10081</v>
+        <v>11031</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>10082</v>
+        <v>11032</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10091</v>
+        <v>12011</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10092</v>
+        <v>12012</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>11011</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>12021</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>11012</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>11021</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>11022</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>12011</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="2" t="s">
+        <v>12022</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>12012</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>12021</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>12022</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>63</v>
+      <c r="C23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF63CA3-83C8-4339-B4B1-16153CBE3C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57BFEC-59EF-410B-B879-91E7C990DC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="1905" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14460" yWindow="1620" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -225,6 +225,18 @@
   </si>
   <si>
     <t>열쇠이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -589,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -782,141 +794,169 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>11011</v>
+        <v>10061</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>11012</v>
+        <v>10062</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>11021</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>11011</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>11022</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>11012</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>11031</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
+        <v>11021</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>11032</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>11022</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>12011</v>
+        <v>11031</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>12012</v>
+        <v>11032</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>12021</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>12011</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
+        <v>12012</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>12021</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>12022</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>42</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57BFEC-59EF-410B-B879-91E7C990DC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D71BF31-8898-4A74-87DD-919FBC5D4977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="1620" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -604,7 +604,7 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
     <col min="3" max="3" width="45.375" customWidth="1"/>
     <col min="4" max="4" width="36.75" customWidth="1"/>
@@ -822,7 +822,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>11011</v>
+        <v>10071</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>25</v>
@@ -836,7 +836,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>11012</v>
+        <v>10072</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>11021</v>
+        <v>10081</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>11022</v>
+        <v>10082</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>30</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>11031</v>
+        <v>10091</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>11032</v>
+        <v>10092</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>46</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>12011</v>
+        <v>10101</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>26</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>12012</v>
+        <v>10102</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>26</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>12021</v>
+        <v>10111</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>42</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>12022</v>
+        <v>10112</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>42</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D71BF31-8898-4A74-87DD-919FBC5D4977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334A9A5B-518E-45CA-A775-EB9639ADE173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9705" yWindow="1575" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>key</t>
   </si>
@@ -237,6 +237,30 @@
   </si>
   <si>
     <t>문이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A locked door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라디오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라디오다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠긴 문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠긴 문이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -601,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -736,18 +760,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>10041</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -755,27 +779,27 @@
         <v>10042</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10051</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
+      <c r="B12" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -783,13 +807,13 @@
         <v>10052</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -797,13 +821,13 @@
         <v>10061</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -811,13 +835,13 @@
         <v>10062</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -825,13 +849,13 @@
         <v>10071</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -839,69 +863,69 @@
         <v>10072</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>10081</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>30</v>
+      <c r="B18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>10082</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>10091</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>48</v>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10092</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>46</v>
+      <c r="B21" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -909,13 +933,13 @@
         <v>10101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -923,40 +947,96 @@
         <v>10102</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>10111</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>42</v>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>10112</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>10121</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>10122</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>10131</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>10132</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>42</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334A9A5B-518E-45CA-A775-EB9639ADE173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C133EE0-09AB-4D94-8311-9D903C98012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9705" yWindow="1575" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13050" yWindow="2520" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
   <si>
     <t>key</t>
   </si>
@@ -261,6 +261,18 @@
   </si>
   <si>
     <t>잠긴 문이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lock</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자물쇠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자물쇠다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -877,13 +889,13 @@
         <v>10081</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -891,69 +903,69 @@
         <v>10082</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>10091</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>30</v>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10092</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>30</v>
+      <c r="B21" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>10101</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
+      <c r="B22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>10102</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -961,13 +973,13 @@
         <v>10111</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -975,13 +987,13 @@
         <v>10112</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -989,13 +1001,13 @@
         <v>10121</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1003,40 +1015,68 @@
         <v>10122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>10131</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>42</v>
+      <c r="B28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>10132</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>10141</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D30" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>10142</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>42</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C133EE0-09AB-4D94-8311-9D903C98012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195E7934-5A95-4854-9EE2-29569ED6AC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="2520" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13365" yWindow="2190" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>key</t>
   </si>
@@ -274,6 +274,9 @@
   <si>
     <t>자물쇠다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HackBox</t>
   </si>
 </sst>
 </file>
@@ -637,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -916,84 +919,84 @@
       <c r="A20" s="3">
         <v>10091</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10092</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>10101</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>30</v>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>10102</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>30</v>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>10111</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
+      <c r="B24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>10112</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
+      <c r="B25" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1001,13 +1004,13 @@
         <v>10121</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1015,13 +1018,13 @@
         <v>10122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1029,13 +1032,13 @@
         <v>10131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1043,40 +1046,68 @@
         <v>10132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>10141</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>42</v>
+      <c r="B30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>10142</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>10151</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>10152</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>42</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195E7934-5A95-4854-9EE2-29569ED6AC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFCB25-D86C-45AF-AD2A-006666F2D278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13365" yWindow="2190" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="3675" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
   <si>
     <t>key</t>
   </si>
@@ -64,14 +64,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>This is a tablet.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타블렛이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>korean</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -170,10 +162,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>어딘가에 던질만한 물건이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Board</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -277,6 +265,22 @@
   </si>
   <si>
     <t>HackBox</t>
+  </si>
+  <si>
+    <t>이 해킹박스의 퍼즐을 풀어 문을열 수 있을 것 같다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽돌을 던져 버튼을 누를 수 있을 것 같다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>update software</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>타블렛 소프트웨어 업데이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -654,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -668,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -682,7 +686,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -696,13 +700,13 @@
         <v>10011</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -710,13 +714,13 @@
         <v>10012</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -724,10 +728,10 @@
         <v>10021</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -738,7 +742,7 @@
         <v>10022</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
@@ -752,13 +756,13 @@
         <v>10031</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -766,13 +770,13 @@
         <v>10032</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
@@ -780,13 +784,13 @@
         <v>10041</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -794,13 +798,13 @@
         <v>10042</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -808,13 +812,13 @@
         <v>10051</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -822,13 +826,13 @@
         <v>10052</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -836,13 +840,13 @@
         <v>10061</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -850,13 +854,13 @@
         <v>10062</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -864,13 +868,13 @@
         <v>10071</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -878,13 +882,13 @@
         <v>10072</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -892,13 +896,13 @@
         <v>10081</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -906,13 +910,13 @@
         <v>10082</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -920,13 +924,13 @@
         <v>10091</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -934,13 +938,13 @@
         <v>10092</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -948,10 +952,10 @@
         <v>10101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -962,13 +966,13 @@
         <v>10102</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -976,13 +980,13 @@
         <v>10111</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -990,13 +994,13 @@
         <v>10112</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1004,13 +1008,13 @@
         <v>10121</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1018,13 +1022,13 @@
         <v>10122</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1032,13 +1036,13 @@
         <v>10131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1046,13 +1050,13 @@
         <v>10132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1060,13 +1064,13 @@
         <v>10141</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1074,13 +1078,13 @@
         <v>10142</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1088,13 +1092,13 @@
         <v>10151</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1102,13 +1106,13 @@
         <v>10152</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CFCB25-D86C-45AF-AD2A-006666F2D278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B34820C-EDD4-4F4A-9A31-FE14070F01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="3675" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-465" yWindow="1875" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="74">
   <si>
     <t>key</t>
   </si>
@@ -80,10 +80,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>It is a battery that can be used for flashlight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>손전등에 사용 가능한 배터리이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,10 +154,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>It's a brick to throw somewhere.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Board</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -224,10 +216,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>문이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Radio</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -248,10 +236,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>잠긴 문이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lock</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -260,17 +244,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>자물쇠다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HackBox</t>
   </si>
   <si>
-    <t>이 해킹박스의 퍼즐을 풀어 문을열 수 있을 것 같다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>벽돌을 던져 버튼을 누를 수 있을 것 같다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -280,6 +256,90 @@
   </si>
   <si>
     <t>타블렛 소프트웨어 업데이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>굳게 잠겨있다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>열쇠로 열 수 있는 자물쇠다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해킹 문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HackingDoor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1D1C1D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잠금잠치에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1D1C1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1D1C1D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접근해야한다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>관련 기능이 부족하다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Access to HackBox.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is a battery that can be used for flashlight.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Throw a brick and press the button.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>You don't have the necessary ability for this interaction.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반대쪽에서만 열 수 있다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It can only be opened on the other side.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is a lock that can be opened with a key.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The door is securely locked.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -290,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +390,26 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -351,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -364,6 +444,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -644,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -658,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -672,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -686,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -700,13 +781,13 @@
         <v>10011</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -714,13 +795,13 @@
         <v>10012</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -728,10 +809,10 @@
         <v>10021</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -742,7 +823,7 @@
         <v>10022</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
@@ -756,13 +837,13 @@
         <v>10031</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -770,13 +851,13 @@
         <v>10032</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
@@ -784,13 +865,13 @@
         <v>10041</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -798,13 +879,13 @@
         <v>10042</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -812,13 +893,13 @@
         <v>10051</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -826,13 +907,13 @@
         <v>10052</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -840,13 +921,13 @@
         <v>10061</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -854,13 +935,13 @@
         <v>10062</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -868,13 +949,13 @@
         <v>10071</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -882,13 +963,13 @@
         <v>10072</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -896,13 +977,13 @@
         <v>10081</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -910,13 +991,13 @@
         <v>10082</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -924,13 +1005,13 @@
         <v>10091</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -938,13 +1019,13 @@
         <v>10092</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -952,10 +1033,10 @@
         <v>10101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -966,13 +1047,13 @@
         <v>10102</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -980,13 +1061,13 @@
         <v>10111</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -994,13 +1075,13 @@
         <v>10112</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1008,13 +1089,13 @@
         <v>10121</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
         <v>43</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1022,13 +1103,13 @@
         <v>10122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1036,10 +1117,10 @@
         <v>10131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>13</v>
@@ -1050,13 +1131,13 @@
         <v>10132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1064,13 +1145,13 @@
         <v>10141</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1078,7 +1159,7 @@
         <v>10142</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
@@ -1092,13 +1173,13 @@
         <v>10151</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1106,13 +1187,41 @@
         <v>10152</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>10161</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>10162</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GametubeGD\Desktop\Github\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B34820C-EDD4-4F4A-9A31-FE14070F01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-465" yWindow="1875" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="465" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>key</t>
   </si>
@@ -56,50 +55,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>This is a table.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>탁자다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>korean</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>She is my…</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그녀는 나의…</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>배터리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>손전등에 사용 가능한 배터리이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>어딘가 이상한 물건이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>There is something strange about it.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>If it falls, it will block the corridor.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것이 넘어지면 복도를 막을 것 같다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Table</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,28 +121,16 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Board</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>드럼통</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>드럼통이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PropaneTank</t>
   </si>
   <si>
     <t>DrumBarrel</t>
   </si>
   <si>
-    <t>This is a drum barrel.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>이상한 물건 이거부숴지는거..</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -196,18 +147,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>This is a Key.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>열쇠</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>열쇠이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Door</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -220,22 +163,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A locked door</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>라디오</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>라디오다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠긴 문</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lock</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -247,86 +178,6 @@
     <t>HackBox</t>
   </si>
   <si>
-    <t>벽돌을 던져 버튼을 누를 수 있을 것 같다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>update software</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타블렛 소프트웨어 업데이트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>굳게 잠겨있다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>열쇠로 열 수 있는 자물쇠다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>해킹 문</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HackingDoor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1D1C1D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잠금잠치에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1D1C1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1D1C1D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>접근해야한다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>관련 기능이 부족하다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Access to HackBox.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>It is a battery that can be used for flashlight.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Throw a brick and press the button.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>You don't have the necessary ability for this interaction.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>반대쪽에서만 열 수 있다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -335,22 +186,58 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>It is a lock that can be opened with a key.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The door is securely locked.</t>
+    <t>Tablet 소프트웨어 업데이트가 필요하다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>You must update your tablet software.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Button Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문이 잠겨있어 열 수 없다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door is Locked.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Locked Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hack Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>힘으로는 열 수 없어 관련 기술이 필요하다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It cannt be opened by force, so related skills are required</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 조건을 만족해야 열리는 문같다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This door can open when certain conditions are met.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,21 +281,17 @@
       <sz val="11"/>
       <color rgb="FF1D1C1D"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -431,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,7 +327,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -724,13 +608,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="45.375" customWidth="1"/>
+    <col min="3" max="3" width="49.75" customWidth="1"/>
     <col min="4" max="4" width="36.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -739,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -753,7 +637,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -767,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -781,448 +665,284 @@
         <v>10011</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>10012</v>
+        <v>10021</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>10021</v>
+        <v>10031</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>10022</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>10041</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>10031</v>
+        <v>10051</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>10032</v>
+        <v>10052</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>10041</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>10053</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>10042</v>
+        <v>10054</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="7" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>10051</v>
+        <v>10055</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>10052</v>
+        <v>10061</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>10061</v>
+        <v>10081</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>10062</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>10091</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>10071</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>10092</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>10072</v>
+        <v>10101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>10081</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>10111</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>10082</v>
+        <v>10121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10091</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
+        <v>10131</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10092</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
+        <v>10141</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>10101</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>10151</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>10102</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A23" s="3"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>10111</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>10112</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>10121</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>10122</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>10131</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>10132</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>10141</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>10142</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>10151</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>10152</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <v>10161</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
-        <v>10162</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="465" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
+    <workbookView xWindow="1395" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -227,6 +227,14 @@
   </si>
   <si>
     <t>This door can open when certain conditions are met.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Locked</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠겼다</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -772,7 +780,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="7" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10055</v>
       </c>
@@ -816,121 +824,129 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>10091</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
+        <v>10082</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>10092</v>
+        <v>10091</v>
       </c>
       <c r="B16" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>10101</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>10092</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>10111</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>10101</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>10121</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
+        <v>10111</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10131</v>
+        <v>10121</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10141</v>
+        <v>10131</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
+        <v>10141</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>10151</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
@@ -947,5 +963,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
+    <workbookView xWindow="2325" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>key</t>
   </si>
@@ -235,6 +235,22 @@
   </si>
   <si>
     <t>잠겼다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 비추면 멈추게 하는 기능이 업데이트 되었다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy stun function is Updated</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hacking function is Updated</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해킹하는 기능이 업데이트 되었다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -245,7 +261,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,13 +302,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,7 +345,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -623,7 +631,7 @@
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
     <col min="3" max="3" width="49.75" customWidth="1"/>
-    <col min="4" max="4" width="36.75" customWidth="1"/>
+    <col min="4" max="4" width="43.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -766,7 +774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10054</v>
       </c>
@@ -780,7 +788,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10055</v>
       </c>
@@ -880,85 +888,101 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>10111</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>18</v>
+        <v>10102</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10121</v>
+        <v>10103</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10131</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>10111</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>10141</v>
+        <v>10121</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
+        <v>10131</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>10141</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>10151</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
+    <workbookView xWindow="3255" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
+    <workbookView xWindow="5115" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>key</t>
   </si>
@@ -238,19 +238,43 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>적을 비추면 멈추게 하는 기능이 업데이트 되었다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy stun function is Updated</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Hacking function is Updated</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>해킹하는 기능이 업데이트 되었다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy Attack function is Updated</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 공격하는 기능이 업데이트 되었다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Save</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Save</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Save</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저장했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saved</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -877,13 +901,13 @@
         <v>10101</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -891,96 +915,124 @@
         <v>10102</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10103</v>
+        <v>11001</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10111</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>11002</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>10121</v>
+        <v>11003</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>10131</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>11011</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>10141</v>
+        <v>11021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>10151</v>
-      </c>
-      <c r="B25" s="5" t="s">
+        <v>11031</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>11041</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>11051</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>26</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTextTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
+    <workbookView xWindow="6045" yWindow="1875" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
   <si>
     <t>key</t>
   </si>
@@ -218,10 +218,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>It cannt be opened by force, so related skills are required</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>특정 조건을 만족해야 열리는 문같다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -238,18 +234,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Hacking function is Updated</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>해킹하는 기능이 업데이트 되었다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy Attack function is Updated</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>적을 공격하는 기능이 업데이트 되었다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -275,6 +263,26 @@
   </si>
   <si>
     <t>Saved</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This SavePoint is already used.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy Attack function is Updated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hacking function is Updated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It cannt be opened by force, so related skills are required.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미 사용된 저장 포인트이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -649,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -806,13 +814,13 @@
         <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="6" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10055</v>
       </c>
@@ -820,7 +828,7 @@
         <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>49</v>
@@ -862,10 +870,10 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
         <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -901,13 +909,13 @@
         <v>10101</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -915,124 +923,138 @@
         <v>10102</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>11001</v>
+        <v>10103</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>11011</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>11003</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>11021</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" t="s">
-        <v>31</v>
+        <v>11011</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>11031</v>
+        <v>11021</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>11041</v>
+        <v>11031</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
+        <v>11041</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
         <v>11051</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>26</v>
       </c>
     </row>
